--- a/backend/missing_cogs_report.xlsx
+++ b/backend/missing_cogs_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:B399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,20 +434,3195 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DW-500 NT 740 DELICIOUS -18LP</t>
-        </is>
-      </c>
+          <t>11-256 AF PU THINNER-30LJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>11-260 AF PU THINNER HD-200LK</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11-260 AF PU THINNER-200LK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-260-1 AF PU THINNER-200LK</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>11-261 AF PU THINNER-200LK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>11-261 AF PU THINNER-20LJ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>16-1015 URT FLAT A ST 01-16KP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16-2005 URT SANDING A VN-200KB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>26-1005 URT FLAT A VN-16KP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>26-4020 URT WHITE A-16KP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>26-4029 URT WHITE A VN-16KP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2K ACRYLIC GREY GLOSS VN-1KS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2K ACRYLIC TRẮNG MỜ VN-1KS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2K ACRYLIC WHITE GLOSS VN-1KS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2K ACRYLIC XÁM XINGFA MỜ VN-1KS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2K ACRYLIC XÁM XINGFA MỜ VN-5KS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2K ACRYLIC ĐEN MỜ VN-5KS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>64-56 MICRO FILLER VN-20KP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>82-1045 UE AF URT FLAT A-16KP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>82-1047 UE AF URT FLAT A-16KP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>82-1099 UE AF URT FLAT A-16KP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>82-1189 UE AF URT FLAT A 5% VN-16KP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>82-2027 UE AF URT SANDING A-16KP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>82-4020 UE AF URT WHITE A-16KP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>82-4169 UE AF URT WHITE A VN-16KP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>82-5001 UE AF URT SFC WHITE A-16KP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A-1000 BASE A-0.9L</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A-1000 BASE A-2.5L</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A-1000 BASE B-2.5L</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A-1000 BASE D-2.5L</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A-1000 BASE D-20LP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A-1000 DOF BASE B-0.9L</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A-1000 SUPER WHITE-9102-0.9L</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AL-088 VN-16KP</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AL-088 VN-4L</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AL-089 VN-16KP</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AL-089 VN-4K</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AL-090 VN-4K</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AZP-481 ZINC PHOSPHATE VN-1K</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AZP-481 ZINC PHOSPHATE VN-4K</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DC-12229 LC BLACK 10 VN-18KP</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DECOR PRIMER AR-300 VN-5L</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DECORLOTUS DI-400 BASE A VN-18LP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DECORSHIELD DW-500 BASE A VN-18LP</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DECORSHIELD DW-500 WHITE VN-18LP</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DECORSHIELD DW-500 WHITE VN-5L</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DI-400 019-1 BELIZE BREEZE-18LP</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DP-12123 LC WHITE 01 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DP-12129 LC BLACK VN-20KP</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DP-12129 LC BROWN 458B KD VN-18KP</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DP-12130 WHITE VN-18KP</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DP-4010 BASE-18LP</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DP-4011 PRIMER-18LP</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DW-500 NT 740 DELICIOUS -18LP</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EDL-601 CARAMEL 8001 VN-4L</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EDL-601 SUNSET YELLOW 3002 VN-4L</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EDL-601 TWILIGHT TEAK 8303 ID VN-4L</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EDL-601 TWILIGHT TEAK 8303 VN-4L</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EDP-551 BLACK (ĐEN) VN-1KS</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EDP-551 BLACK (ĐEN) VN-5KS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EDP-551 DARK GREY (XÁM XINGFA) VN-1KS</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EDP-551 DARK GREY (XÁM XINGFA) VN-5KS</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EDP-551 WHITE (TRẮNG) VN-5KS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EDP-551 ZINC PHOSPHATE (XÁM) VN-1KS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EDP-551 ZINC PHOSPHATE (XÁM) VN-20KSP</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EDP-551 ZINC PHOSPHATE (XÁM) VN-5KS</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EL-501 CARAMEL 8001 VN-1L</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EL-501 CARAMEL 8001 VN-4L</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EL-501 CHERRY RED 3002 VN-1L</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EL-501 CHERRY RED 3002 VN-4L</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EL-501 CHOCOLATE 8303 VN-4L</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EL-501 CLASSIC TEAK 8305 VN-1L</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EL-501 LS BLACK 9001 VN-1L</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EL-501 LS BLACK 9001 VN-4L</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EL-501 LS CANDY BROWN 1002 VN-4L</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EL-501 LS COCOA BROWN 2003 VN-1L</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EL-501 LS COCOA BROWN 2003 VN-4L</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EL-501 LS COFFEE BROWN 8004 VN-1L</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EL-501 LS RED MAHONY 3005 VN-1L</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EL-501 NATURAL DOF 0014 VN-1L</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EL-501 NATURAL DOF 0014 VN-4L</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EL-501 NATURAL GLOSS 0015 VN-1L</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>EL-501 NATURAL GLOSS 0015 VN-4L</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EL-501 NATURAL SATIN 0016 VN-1L</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EL-501 NATURAL SATIN 0016 VN-4L</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EL-501 SUNSET YELLOW 2011 VN-1L</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>EL-501 TROPICAL TEAK 8012 VN-4L</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EL-501 WALNUT 9013 VN-1L</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>GZ-12700 N BLACK VN-4K</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GZ-12700 N STRATON KD VN-18KP</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>GZ-12700 N YELLOW-4K</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>GZ-9127-N-BL-AK-4K</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>GZ-9127-N-RE-AK-4K</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>GZ-9127-N-YE-AK-4K</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>GZPU-21500 BLACK VN-4K</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>GZPU-21500 BROWN VN-4K</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>GZPU-21500 HV 03 VC III VN-18KP</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>GZPU-21500 HV 04 VC III VN-18KP</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>GZPU-21500 HV 04 VC VN-18KP</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>GZPU-21500 HV 13 VC VN-18KP</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>GZPU-21500 YELLOW VN-4K</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>HARDENER PUH-74 SD VN-16KP</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>HARDENER PUH-74 SD VN-1K</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>HARDENER PUH-74 SD VN-4K</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>HARDENER PUH-75 NY VN-0.2K</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>HARDENER PUH-75 NY VN-4K</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LOL-1762-01-AK-180KK</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MEP-12003 BROWN KI VN-18KP</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MEP-12003 CLEAR BASE VN-18KP</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MEP-12003 GREY VN-18KP</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MEPH-12003 PS VN-2K</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MPUC-13600 TEXTURE BROWN KI VN-16KP</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MPUL-13700 90 VN-16KP</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MPULH-13700 PS VN-4K</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MX-94 VC TRAFFIC YELLOW VN-20KSP</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MX-99 IVORY VN-1KS</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>NBC-9345-706-AK-200KB</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>NBC-9345-787-AK-20KP</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>NBC-9345-802-AK-200KB</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>NCL-1113-29 LC 10 AK-20LP</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>NCL-1113-29 LC 25 AK-20LP</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>NCL-1113-29 LC 5 AK-20LP</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>NCL-1113-SR05AK-18KP</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>NCL-1113-SR10AK-18KP</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>NCL-11329 LC CLEAR 05 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NCL-11329 LC CLEAR 10 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>NCL-11329 LC CLEAR 20 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>NCL-11329 LC CLEAR 30 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>NCL-11329 LC CLEAR 50 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NCL-40800 LC MOD CLEAR 20 VN-18KP</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>NCL-40800 LY CLEAR 10 VN-18LP</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NCL-9408-20-AK-180KB</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NCSS-1112-29 LC AK-200LB</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NCSS-11229 LC VN-20LP</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>NCSS-11229 VT VN-18KP</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>NCSS-30800 LC MOD VN-20LP</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>NCSS-30800 LY MOD VN-18KP</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>NCSS-9308-LC-AK-180KB</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>P-01 SOLAR RED 2006 VN-1L</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>P-01 SOLAR YELLOW 1007 VN-1L</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>PC 8B2-1L</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>PC 8G1-1L</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>PC 8K2-1L</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>PC 8R2-1L</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PC 8W1-1L</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PC 8Y3-1L</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>PCA-31100 BLACK OB PASTE AF VN-4K</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>PCA-31100 BLACK PASTE AF VN-4K</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PCA-31100 BLACK PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PCA-31100 BLUE OG PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PCA-31100 BROWN 645 PASTE AF VN-4K</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PCA-31100 BROWN 645 PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PCA-31100 OXIDE RED PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PCA-31100 RED OB 35 PASTE AF VN-4K</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PCA-31100 RED OB 35 PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>PCA-31100 RX C50 BLACK VN-18KP</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>PCA-31100 WHITE PASTE AF VN-4K</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PCA-31100 WHITE PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PCA-31100 YELLOW HR PASTE AF VN-4K</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PCA-31100 YELLOW HR PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>PCA-31100 YELLOW OG 16 PASTE AF VN-4K</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>PCA-31100 YELLOW OG 16 PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PCA-31100 YELLOW OKER PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PCL-31300 BLACK PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>PCL-31300 BLACK PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>PCL-31300 BLUE OG PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>PCL-31300 BLUE OR 50 PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PCL-31300 BLUE OR PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PCL-31300 BROWN PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>PCL-31300 OXIDE RED PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PCL-31300 RED 31701 PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PCL-31300 RED OB 35 PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PCL-31300 VIOLET PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PCL-31300 WHITE PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>PCL-31300 YELLOW 170 HR PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PCL-31300 YELLOW OG 16 PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PCL-31300 YELLOW OKER PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PCWB-31600 BROWN 645 PASTE VN-4K</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PCWB-31600 OXIDE YELLOW PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>PCWB-31601 BLACK OB PASTE-4K</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PFP-241 VN-20KSP</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>PFP-251-2K SF VN-15KSP</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>PFT-215 LIGHT GREY VN-21KSP</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PFT-253 AVOCADO VN-20KSP</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t>PFT-253 QUARTZ GREY RAL 7039 VN-20KSP</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>PG-13900 WHITE 01 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>PG-13900 WHITE W03 F1 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>PRCC-10351 WBC POLYESTER TOA-250KK</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>PRCC-10361 WBC POL HV TQ VN-20KP</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>PRCC-20312 POL VARNISH CANPAC-200KK</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>PRCC-40102 HV CLEAR LACQUER CL VN-200KK</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PRCC-40102 HV GOLD T350 CT VN-200KK</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>PROPAN HWO-558-1L</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>PST-12100 BRO W03 DAM F1 VN-16KJ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>PST-12100 C10 RED VN-4K</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PST-12100 C10 YELLOW VN-4K</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>PST-12100 C20 WHITE-4K</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>PST-12100 YEL W03 LAU F1 VN-16KJ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>PST-12202 BROWN SC VN-200LK</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PST-12202 MUB SC VN-200LK</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PSV-76000 SB HC MY VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PUC-52239 WHITE 10 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PUC-52239 WHITE 30 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>PUC-54205 AC KEM3234P 08 HPT VN-20KP</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>PUC-54205 AC WHITE 10 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>PUC-54205 AC WHITE 15 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>PUC-54205 AC WHITE 50 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>PUC-54205 AC WHITE 90 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>PUC-54205 AC WHITEGREY 05 MK VN-20KP</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>PUC-756 NY TRẮNG BÓNG 100% VN-0.8K</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>PUC-756 NY TRẮNG MỜ 100% VN-16KP</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PUC-756 NY TRẮNG MỜ 70% VN-16KP</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>PUC-786-2K SATIN BASE A*-5LS</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>PUH-1561-33-AK-20KP</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>PUH-56133 S VN-20KP</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>PUH-56135 S VN-20KP</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>PUH-56135 S VN-4K</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>PUH-56139 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>PUH-56141 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>PUH-56142 SP VN-20KP</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>PUH-56303 NY VN-20KP</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>PUH-56306 LY VN-20LP</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>PUL-51333 CLEAR 20 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>PUL-51333 CLEAR 40 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>PUL-51333 CLEAR 60 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>PUL-51335 CLEAR 10 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>PUL-51335 CLEAR 30 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>PUL-51337 CLEAR 50 VN-18KP</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>PUL-51339 CLEAR 10 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>PUL-51341 CLEAR 05 VN-18KP</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>PUL-51341 CLEAR 10 VN-18KP</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PUL-53306 AC EX CLEAR 05 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PUL-53306 AC EX CLEAR 10 AA VN-20LP</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PUL-53306 AC EX CLEAR 10 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PUL-53306 AC EX CLEAR 20 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PUL-53306 AC EX CLEAR 30 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>PUL-53306 AC EX CLEAR 40 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>PUL-53306 AC EX CLEAR 90 VN-20LP</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>PUL-745 2K MỜ 100% VN-16KP</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>PUL-745 2K MỜ 50% VN-16KP</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>PUL-745 2K MỜ 70% VN-16KP</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>PUL-745 2K MỜ 70% VN-4K</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>PUL-765 2K BÓNG 100% VN-1KS</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>PUL-765 2K MỜ 50% VN-1KS</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>PUL-765 2K MỜ 50% VN-5KS</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>PUL-765 2K MỜ 70% VN-1KS</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>PUL-765 2K MỜ 90% VN-1KS</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>PUL-765 2K MỜ 90% VN-5KS</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>PUL-765-2K DOF BASE D-5LS</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>PUL-765-2K GLOSS BASE D-5LS</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>PUL-765-2K SATIN BASE D-5LS</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>PUP-1521-570-AK-200KB</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>PUP-1521-697-AK-20KP</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>PUP-52122 PUTTY VN-4K</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>PUP-52135 BLACK VN-20KP</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>PUP-52135 WHITE VN-200KB</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>PUP-52135 WHITE VN-20KP</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>PUP-52141 WHITE 01 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>PUP-52142 ACR WHITE SP VN-20KP</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>PUP-54111 AC WHITE VN-20KP</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>PUP-752-2K WHITE VN-16KP</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>PUSF-781 2K LÓT TRẮNG VN-5KS</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>PUSS-51235 VN-200KB</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>PUSS-51235 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>PUSS-51241 VC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>PUSS-51241 VN-200KB</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>PUSS-51241 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>PUSS-53206 AC EX STB VN-20KP</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>PUSS-53206 AC EX VN-20KP</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>PUSS-740-2K VT VN-1K</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>PUSS-740-2K VT VN-4K</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>PUSS-760 2K LÓT TRONG VN-1KS</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>RD-74106 VN-200LK</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>RD-74106 VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>SPE-9110 CRACKING VN-4L</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SST-11100 03 VC VN-200LK</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>SST-11100 04 VC III VN-180KK</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>SST-11100 05 VC VN-200LK</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>SST-11100 10 VC III VN-160KK</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>SST-11100 13 VC VN-160KK</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SST-11100 BROWN AA VN-4K</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>SST-11100 C10 BLACK-16KJ</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>SST-11100 C10 BLACK-4K</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>SST-11100 C10 BLUE-16KJ</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>SST-11100 C10 BLUE-4K</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>SST-11100 C10 ORANGE-4K</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>SST-11100 C10 RED-16KJ</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>SST-11100 C10 RED-4K</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SST-11100 C10 YELLOW-4K</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>SST-11100 CAM 14 VC III VN-160KK</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SST-11100 YELLOW KD VN-16KJ</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>SST-2111-BL-AK-4K</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>SST-2111-RED-AK-4K</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SST-2111-YEL-AK-4K</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>SUPER GOLD SG-07 WB GOLD-1230-0.5L</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>SUPER GOLD SG-07 WB GOLD-1230-0.9L</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>TENNOKOTE 1000 WA BASE A-25KSP</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>TENNOKOTE 1000 WA BASE A-5KS</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>TENNOKOTE 1000 WA BASE D-25KSP</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>TENNOKOTE 1000 WA BASE D-5KS</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>THC-2731-201-AK-160KK</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>THC-2731-402-AK-170KK</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>THC-73100 202 VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>THC-73100 402 VN-200LK</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>THC-73100 402 VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>THC-73100 602 RB VN</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>THC-73100-007 VN-200LK</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>THC-73100-007 VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>THC-73100-1103 KD VN-200LK</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>THC-73100-1103 KD VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>THC-73100-1103 VN-200LK</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>THC-73100-201 VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>THC-73100-452 VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>THC-73100-552 VN-18KJ</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>THGZ-2722-AK-150KK</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>THGZ-72200 PU VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>THGZ-72200 VN-200LK</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>THGZ-72200 VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>THINNER PU-047 VT VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>THNC-2711-SD-AK-160KK</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>THNC-71100 SD VN-200LK</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>THNC-71100 SD VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>THPU-71300 SB VN-200LK</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>THPU-71306 01 KD VN-200LK</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>THPU-71306 ST VN-200LK</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>THPU-71306 ST VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>THPU-71306 VN-200LK</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>THPU-71306 VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>THPU-71306-200LK</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>THPU-71324-1 EST YJ VN-200LK</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>TOL-76301 N 2C-03  F1 VN-16KJ</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>TOL-76301 N CLEAR BASE VN-20LJ</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>U-PROOF U-93 BASE A-20KP</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>U-PROOF U-93 BASE C-20KP</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>U-PROOF U-93 LIGHT GREY VN-20KP</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>U-PROOF U-93 LIGHT GREY VN-6K</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>UFM-930 BASE D-1K</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>UFM-930 LIGHT GREY VN-1K</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>UFM-930 LIGHT GREY VN-20KP</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>UFM-930 LIGHT GREY VN-6K</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>UFM-930 LIGHT GREY-1K</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>UFM-930 LIGHT GREY-20KP</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>UFM-930 LIGHT GREY-4K</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>UFM-930 WHITE-1K</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>UFM-930 WHITE-20KP</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>UFM-930 WHITE-4K</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>UPR-960 BASE A VN-20KP</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>UPR-960 BASE B VN-20KP</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>UPR-960 BASE B VN-6K</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>UPR-960 BASE D VN-1K</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>UPR-960 BASE D VN-20KP</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>UPR-960 BASE D VN-6K</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>UPR-960 WHITE 9101 VN-6K</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>UVF-10301 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>UVF-10501 LY VN-20KP</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>UVL-50101 CLEAR 60 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>UVL-50101 CLEAR 90 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>UVL-50101 SR CLEAR 10 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>UVL-50101 SR CLEAR 20 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>UVL-50508 LY CLEAR 08 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>UVP-60301 WHITE VN-20KP</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>UVP-60503 EC GMR SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>UVP-60503 EC LTAP SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>UVP-60508 BLK 01 SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>UVP-60508 DGRY SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>UVP-60508 GMR SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>UVP-60508 SLP NEW SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>UVP-60508 TSG SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>UVP-60508 WHITE SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>UVP-60508 WTEA SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>UVS-20602 TSG 01 SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>UVS-20602 TSG 02 SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>UVS-20602 TSG 03 SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>UVS-20602 WTEA 01 SC VN-5K</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>UVS-20602 WTEA 02 SC VN-5K</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>UVS-20602 WTEA 03 SC VN-5K</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>UVSS-40502 LY VN-20KP</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>V-09 CLEAR GLOSS 0007 VN-0.8L</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>V-09 LIGHT TEAK 3002 VN-0.8L</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>V-09 LIGHT YELLOW 1001 VN-0.8L</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>V-09 MANGGIS 8303 VN-0.8L</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>V-09 REDDISH CLAY 2004 VN-0.8L</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>V-09 TOBACCO 8206 VN-0.8L</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>WBC-1622-BL10AK-20KP</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>WBH-69100 EX-1L</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>WBL-63215 EX BASE VN-20KP</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>WBL-63215 EX CLEAR 20 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>WBL-63220 BLACK 2C01 F1 VN-18KP</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>WBL-63220 BROWN 2C01 N F1 VN-18KP</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>WBMG-97100-1 VN-4K</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>WBP-1621-35W-AK-20KP</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>WBP-1621-BL-AK-20KP</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>WBP-1621-BR-AK-20KP</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>WBP-64115 CSN SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>WBP-64115 GMR SC VN-20KP</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>WBS-224-1K WB-20KJ</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>WFPU-51000 VN-20KP</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>WPWB-81201 W MQ VN-20KP</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
